--- a/artfynd/A 30587-2021 artfynd.xlsx
+++ b/artfynd/A 30587-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30587-2021 artfynd.xlsx
+++ b/artfynd/A 30587-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>98151202</v>
+        <v>98151288</v>
       </c>
       <c r="B24" t="n">
-        <v>78569</v>
+        <v>81236</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633678.1786065999</v>
+        <v>633580.3497755034</v>
       </c>
       <c r="R24" t="n">
-        <v>6977325.522857251</v>
+        <v>6977214.267440598</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3261,7 +3261,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>98151288</v>
+        <v>98151289</v>
       </c>
       <c r="B25" t="n">
         <v>81236</v>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>633580.3497755034</v>
+        <v>633657.1532905163</v>
       </c>
       <c r="R25" t="n">
-        <v>6977214.267440598</v>
+        <v>6977303.212100328</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>98151289</v>
+        <v>98151264</v>
       </c>
       <c r="B26" t="n">
-        <v>81236</v>
+        <v>73631</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,25 +3385,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633657.1532905163</v>
+        <v>633661.985408856</v>
       </c>
       <c r="R26" t="n">
-        <v>6977303.212100328</v>
+        <v>6977330.337307277</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3459,6 +3459,11 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,10 +3490,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>98151264</v>
+        <v>98150981</v>
       </c>
       <c r="B27" t="n">
-        <v>73631</v>
+        <v>77541</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3497,25 +3502,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3525,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>633661.985408856</v>
+        <v>633749.4615691418</v>
       </c>
       <c r="R27" t="n">
-        <v>6977330.337307277</v>
+        <v>6977292.383667613</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3573,11 +3578,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3599,118 +3599,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>98150981</v>
-      </c>
-      <c r="B28" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>185</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Olleberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>633749.4615691418</v>
-      </c>
-      <c r="R28" t="n">
-        <v>6977292.383667613</v>
-      </c>
-      <c r="S28" t="n">
-        <v>25</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
